--- a/output/pdf_financials_xlsx/GRUV.xlsx
+++ b/output/pdf_financials_xlsx/GRUV.xlsx
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009533</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.848452</v>
+        <v>-1.857985</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.273009</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.848452</v>
+        <v>-1.857985</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.273009</v>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008099</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.424413</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.33023</v>
       </c>
     </row>
     <row r="35">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008099</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.424413</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.33023</v>
       </c>
     </row>
     <row r="37">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRUV.xlsx
+++ b/output/pdf_financials_xlsx/GRUV.xlsx
@@ -3563,7 +3563,11 @@
           <t>Proceeds from issue of private placement (note 4)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -3916,7 +3920,11 @@
           <t>Proceeds from issue of private placement</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
